--- a/test1/test1_bom.xlsx
+++ b/test1/test1_bom.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -483,8 +483,6 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="15"/>
-    <col width="90" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -525,45 +523,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Manufacturer</t>
+          <t>MPN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MPN</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Distributor</t>
+          <t>Datasheet URL</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>voltai chat url</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Distributor P/N</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Datasheet URL</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>voltai chat url</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Parts Agent Prompt</t>
         </is>
@@ -603,30 +581,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Unconventional AI</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
           <t>Blackbox component; no part datasheet available yet. Pin/electrical spec source = "[External] Bobcat Board Design.pdf" in project root. Symbol must be generated from the PDF pinout (page 4).</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>N/A — DUT is customer-specified, not selected via parts agent.</t>
         </is>
@@ -664,19 +627,19 @@
           <t>VQFN-20 3.5x3.5 mm</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>TPS7A8401A</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c8197ccb-dda7-4981-945a-5421015597a2</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Already selected. Confirm orderable variant (RGW vs RGR) and stock.</t>
         </is>
@@ -714,23 +677,19 @@
           <t>SOT-23-6 or smaller</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>TPS22916CNYFPR</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c8197ccb-dda7-4981-945a-5421015597a2</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Select a single-channel load-switch IC.
 Electrical:
@@ -785,23 +744,19 @@
           <t>SOIC-8 or smaller</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Microchip 24AA08-I/SN</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/6cc174c7-7609-4275-b027-d92af3ec1cf1</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Select a serial EEPROM.
 Memory:
@@ -853,27 +808,23 @@
           <t>small SMT</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>MCP4728</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/7752d707-71d0-4259-a5e1-afce078ac071</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Uses 2 of 4 channels (BIAS0, BIAS1). External VREF pin tied to 3.3V (NOT internal 2.048V ref). EEPROM programmed to 0xFFF at bring-up -&gt; V_OUT=3.3V -&gt; PMOS off -&gt; 0 uA at POR. See decision log 2026-05-24 bias-polarity-fix.</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Select an I2C-controlled programmable current source / current-output DAC.
 Output:
@@ -927,23 +878,23 @@
           <t>MSOP-8 or smaller</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>OPA2388</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/76ff4f5e-ad1a-4dc1-96ef-177ca5fd3e32</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Alternates: MCP6V52 (auto-zero, MSOP-8); TLV9002 (~0.5% accuracy fallback). OPA2376 Voltai pick superseded by OPA2388 per design decision.</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Select a precision op-amp used in a high-side transconductance current-source loop.
 Topology: V_DAC drives the non-inverting input. The inverting input connects to the source of a PMOS transistor and through a sense resistor R_sense to 3.3 V. The op-amp output drives the PMOS gate. The PMOS drain delivers the regulated output current.
@@ -994,27 +945,23 @@
           <t>SOT-23 or smaller</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>PMZ1200UPEYL</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/76ff4f5e-ad1a-4dc1-96ef-177ca5fd3e32</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Restored to PMOS per bias-polarity fix 2026-05-24. Topology is HIGH-SIDE current source (current INTO BIASx). Alternate: any logic-level PMOS in SOT-23/SOT-666 with |Vgs(th)|&lt;=2V.</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Select a small-signal P-channel MOSFET for a high-side linear current-source pass element.
 Topology: source tied to 3.3 V through a small sense resistor; gate driven by an op-amp output; drain delivers regulated current to an external load that may sit anywhere from 0 V to about 1 V.
@@ -1063,27 +1010,23 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>TNPW06035K11BEEA</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/795d1f84-2210-4cc0-96cc-0f19ebd34a16</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Resized for PMOS high-side topology. I = (3.3V - V_DAC) / R_sense. I_FS at V_DAC=0: 3.3V/5.11k = 646 uA. I_min at V_DAC=3.3V: 0 uA. 12-bit step ~= 0.16 uA at full range. Replaces 3.16 kOhm sized for NMOS low-side.</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Select a precision thin-film chip resistor used as a V-to-I sense element in a transconductance bias loop (high-side PMOS topology).
 Requirements:
@@ -1130,27 +1073,23 @@
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2N7002</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Optional / DNP. Series NMOS pass switch between Q1/Q2 PMOS drain and BIASx jumper. GPIO low at reset -&gt; NMOS off -&gt; hard output isolation independent of MCP4728 EEPROM state. Uses same 2N7002 as last-resort Q1/Q2 footprint stuffing.</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Optional / DNP. Series NMOS pass switch between Q1/Q2 PMOS drain and BIASx jumper. GPIO low at reset -&gt; NMOS off -&gt; hard output isolation independent of MCP4728 EEPROM state. Uses same 2N7002 as last-resort Q1/Q2 footprint stuffing.</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1184,27 +1123,27 @@
           <t>edge or vertical TH</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>HRM(G)-300-467B-1</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>HRM(G)-300-467B-1</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="3" t="inlineStr">
+          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>voltai originally misreported parts with incorrect form fit. Linear submitted</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Select a board-mount SMA connector (RF coaxial, 50 ohm).
 Mechanical:
@@ -1256,31 +1195,27 @@
           <t>FMC LPC, SMT</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>ASP-134606-01</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/40f6d198-5134-4631-b282-00b3c277e681</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>claude + voltai explicitely agree</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Select the mezzanine-side connector for a VITA 57.1 FMC LPC daughtercard.
 Standard:
@@ -1333,27 +1268,23 @@
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TSW-104-05-G-S </t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/0392393d-3cf6-4da0-84d7-844a046d3b4a</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/0392393d-3cf6-4da0-84d7-844a046d3b4a</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Select a 1x4 single-row male pin header.
  - Pitch: 2.54 mm (100 mil).
@@ -1400,31 +1331,27 @@
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Samtec TSW-102-05-G-S</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/ff158635-ccae-4b2a-bb23-3b555f7c5980</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Same as TSW-104-05-G-S </t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Select a 1x2 (2-position, 1-row) male pin header AND its mating shunt cap.
  - Pitch: 2.54 mm (100 mil).
@@ -1469,27 +1396,19 @@
           <t>0603 or 0805</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>CC0805KFX7R6BB106</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Murata GRM21BR71A106KA73L</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/UPY-GPHC_X7R_6_3V-TO-250V</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1535,23 +1454,19 @@
           <t>0402 or 0603</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Murata GRM155R70J105KA12D</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1597,23 +1512,19 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Murata GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1659,23 +1570,19 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>CRCW04020000Z0ED</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/e48a1fc5-00ab-4e0e-bf42-722ef3d0c8b3</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/e48a1fc5-00ab-4e0e-bf42-722ef3d0c8b3</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Select 0 ohm chip jumper resistors.
  - Value: 0 ohm.
@@ -1718,23 +1625,19 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/a7abae63-cf40-4112-8c64-a6d94005f3d7</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/a7abae63-cf40-4112-8c64-a6d94005f3d7</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Select 10 kOhm chip pull-up / pull-down resistors.
  - Value: 10 kOhm.
@@ -1778,27 +1681,23 @@
           <t>TH loop</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Keystone 5011</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c83ca0b9-08f0-4eb9-ac52-96f2abbe4c17</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>claude suggested better part for this Keystone 5011 ×4</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Select PCB-mount GND test points / test loops.
  - Mount: through-hole.
@@ -1811,26 +1710,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" display="https://agent2.demo.voltai.ai/GLOBAL/admin/chat/76ff4f5e-ad1a-4dc1-96ef-177ca5fd3e32" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" display="https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" display="https://suddendocs.samtec.com/catalog_english/tsw_th.pdf" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId18"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test1/test1_bom.xlsx
+++ b/test1/test1_bom.xlsx
@@ -2,21 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Refdes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,25 +27,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,8 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,25 +55,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,17 +79,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -470,19 +445,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="90" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -531,7 +507,7 @@
           <t>Datasheet URL</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>voltai chat url</t>
         </is>
@@ -548,54 +524,52 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>U0</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>DUT (test chip)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Bobcat — custom mixed-signal test chip (Unconventional AI). Device under test for this carrier board.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bobcat - custom mixed-signal test chip (Unconventional AI). Device under test for this carrier board.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>40-QFN, 5x5 mm, 0.4 mm pitch, exposed GND pad (pin 41)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>QFN-40 5x5 mm</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Bobcat</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Blackbox component; no part datasheet available yet. Pin/electrical spec source = "[External] Bobcat Board Design.pdf" in project root. Symbol must be generated from the PDF pinout (page 4).</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>N/A — DUT is customer-specified, not selected via parts agent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="216" customHeight="1">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>N/A - DUT is customer-specified, not selected via parts agent. Blackbox component; no part datasheet available yet. Pin/electrical spec source = '[External] Bobcat Board Design.pdf' in project root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -632,20 +606,16 @@
           <t>TPS7A8401A</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c8197ccb-dda7-4981-945a-5421015597a2</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Already selected. Confirm orderable variant (RGW vs RGR) and stock.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="180" customHeight="1">
+    <row r="4" ht="216" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -677,18 +647,10 @@
           <t>SOT-23-6 or smaller</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>TPS22916CNYFPR</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c8197ccb-dda7-4981-945a-5421015597a2</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Select a single-channel load-switch IC.
@@ -712,7 +674,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="204" customHeight="1">
+    <row r="5" ht="180" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -744,18 +706,10 @@
           <t>SOIC-8 or smaller</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Microchip 24AA08-I/SN</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/6cc174c7-7609-4275-b027-d92af3ec1cf1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Select a serial EEPROM.
@@ -776,7 +730,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="192" customHeight="1">
+    <row r="6" ht="240" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -805,44 +759,35 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>small SMT</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>MCP4728</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/7752d707-71d0-4259-a5e1-afce078ac071</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Uses 2 of 4 channels (BIAS0, BIAS1). External VREF pin tied to 3.3V (NOT internal 2.048V ref). EEPROM programmed to 0xFFF at bring-up -&gt; V_OUT=3.3V -&gt; PMOS off -&gt; 0 uA at POR. See decision log 2026-05-24 bias-polarity-fix.</t>
-        </is>
-      </c>
+          <t>MSOP-10 or smaller</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Select an I2C-controlled programmable current source / current-output DAC.
-Output:
- - Sources current into an external load (load develops voltage across itself).
- - Programmable range: must cover 0 to 640 uA full scale.
- - Resolution: approximately 1 uA per step over the 0-640 uA range (&gt;=10-bit effective).
- - Nominal operating point: 320 uA delivered into a load developing ~0.5 V.
- - Output compliance voltage: &gt;=1.0 V (load may swing from 0 V to &gt;=1 V).
- - Default state at power-up: output OFF / Hi-Z / 0 uA. Output must NOT drive any current until the host writes an enable register. This is a hard requirement.
- - Full-scale accuracy: &lt;=2% preferred.
+          <t>Select an I2C-controlled voltage-output DAC to drive a high-side PMOS transconductance bias loop.
+Topology context:
+ - The DAC drives the non-inverting input of an external precision op-amp.
+ - The op-amp output drives the gate of a PMOS pass transistor.
+ - The PMOS source connects to 3.3V through a sense resistor R_sense; the source node also feeds the op-amp inverting input.
+ - The PMOS drain delivers regulated current INTO the test-chip bias pin via a 1x2 jumper.
+ - I_load = (3.3 V - V_DAC) / R_sense.
+Requirements:
+ - Resolution: &gt;=12-bit preferred (10-bit minimum) for ~1 uA resolution over 0-640 uA full scale.
+ - Output swing: rail-to-rail at 3.3 V supply; MUST be able to reach the positive rail (~3.3 V) to fully shut off the PMOS and reach 0 uA at the low end.
+ - External voltage reference input required (or selectable) so V_REF = 3.3 V can be used; do not rely on a 2.048 V internal reference.
+ - Default state at power-up: output at the positive rail (PMOS off). Must be programmable for default-off behavior (EEPROM default code = 0xFFF or equivalent).
+ - Settling time: &lt;1 ms acceptable; control loop sets bandwidth.
 Interface:
  - I2C, standard or fast mode.
- - Hardware-selectable address pins preferred (two devices share the same bus).
+ - Hardware-selectable address pins preferred.
 Supply: 3.3 V single supply.
-Channels: single-channel acceptable (two devices needed for BIAS0 and BIAS1) OR a 2-channel device with fully independent per-channel control.
-Package: any small SMT (SOT-23, MSOP, DFN, QFN, etc).
-Temperature: -40 C to +85 C minimum.
-Context: provides bias current to two analog input pins of a custom test chip. Output routes through a 1x2 jumper to the bias pin so the source can be physically isolated.</t>
+Channels: 2 channels needed total (BIAS0 and BIAS1). A 2-channel or higher device acceptable.
+Package: any small SMT.
+Temperature: -40 C to +85 C minimum.</t>
         </is>
       </c>
     </row>
@@ -865,7 +810,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Dual precision RRIO op-amp; closes transconductance loop for V-to-I bias source</t>
+          <t>Dual precision RRIO op-amp; closes high-side PMOS transconductance loop</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -878,42 +823,30 @@
           <t>MSOP-8 or smaller</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>OPA2388</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/76ff4f5e-ad1a-4dc1-96ef-177ca5fd3e32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Alternates: MCP6V52 (auto-zero, MSOP-8); TLV9002 (~0.5% accuracy fallback). OPA2376 Voltai pick superseded by OPA2388 per design decision.</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Select a precision op-amp used in a high-side transconductance current-source loop.
-Topology: V_DAC drives the non-inverting input. The inverting input connects to the source of a PMOS transistor and through a sense resistor R_sense to 3.3 V. The op-amp output drives the PMOS gate. The PMOS drain delivers the regulated output current.
+Topology: V_DAC drives the non-inverting input. A PMOS pass transistor has its source connected to 3.3 V through a sense resistor R_sense; that source node also feeds the op-amp inverting input. The op-amp output drives the PMOS gate. The PMOS drain delivers the regulated output current INTO the test-chip bias pin.
 Requirements:
  - Single supply operation at 3.3 V.
- - Rail-to-rail input AND rail-to-rail output, both required (output must be able to drive PMOS gate close to either rail to turn it fully off and fully on).
- - Input offset voltage (Vos): &lt;=1 mV maximum. This is critical for accuracy at the low end of the output current range (~1-10 uA).
+ - Rail-to-rail input AND rail-to-rail output, both required (output must drive PMOS gate close to either rail to turn it fully off and fully on).
+ - Input offset voltage (Vos): &lt;=0.5 mV maximum. Critical for accuracy at the low end of bias current (~1-10 uA).
  - Input bias current: &lt;=1 nA typical (CMOS / FET input stage).
- - Input common-mode range must include both rails (or at least include the expected V_DAC range, 0-3.3 V).
+ - Input common-mode range must include both rails (sees V_sense which sits near 3.3 V at low bias currents).
  - Gain-bandwidth product: &gt;=1 MHz.
- - Unity-gain stable; capable of driving a capacitive load (PMOS gate, typically tens to hundreds of pF) without oscillation. Internal compensation for capacitive loads preferred, or specify Cload tolerance.
+ - Unity-gain stable; capable of driving a MOSFET gate (tens to hundreds of pF) without oscillation.
  - Quiescent current: &lt;500 uA per channel preferred.
-Channels: 2 channels needed total (one per bias source). Dual-channel device or two singles both acceptable.
+Channels: 2 channels needed total (one per bias source). Dual-channel device preferred.
 Package: any small SMT (SOT-23-5, SC-70-5, MSOP-8, DFN-8).
 Temperature: -40 C to +85 C minimum.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="144" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -932,7 +865,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Small-signal logic-level P-channel MOSFET pass element; source through R_sense to 3.3V, drain to BIASx (high-side current source)</t>
+          <t>Small-signal logic-level P-channel MOSFET pass element; high-side current source into BIASx</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -942,43 +875,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>SOT-23 or smaller</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>PMZ1200UPEYL</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/76ff4f5e-ad1a-4dc1-96ef-177ca5fd3e32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Restored to PMOS per bias-polarity fix 2026-05-24. Topology is HIGH-SIDE current source (current INTO BIASx). Alternate: any logic-level PMOS in SOT-23/SOT-666 with |Vgs(th)|&lt;=2V.</t>
-        </is>
-      </c>
+          <t>SOT-23 or SOT-666</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Select a small-signal P-channel MOSFET for a high-side linear current-source pass element.
-Topology: source tied to 3.3 V through a small sense resistor; gate driven by an op-amp output; drain delivers regulated current to an external load that may sit anywhere from 0 V to about 1 V.
+Topology: source connected to 3.3 V through a small sense resistor; gate driven by an op-amp output; drain delivers regulated current INTO the test-chip bias pin (drain sits anywhere from ~0 V to ~1 V depending on chip load).
 Requirements:
- - Vds breakdown (Vds_max): &gt;=6 V (operates at &lt;=3.3 V Vds with margin).
- - Vgs(th): logic-level threshold preferred; |Vgs(th)| &lt;= 2 V so the device fully enhances within the 3.3 V gate-drive range.
+ - Vds breakdown (Vds_max): &gt;=6 V.
+ - |Vgs(th)|: logic-level threshold; |Vgs(th)| &lt;= 2 V so the device fully enhances within the 3.3 V gate-drive range.
  - Continuous drain current rating: &gt;=10 mA (operates at &lt;=1 mA so any small-signal device is fine).
  - Rds(on): not critical (linear-region operation, op-amp closes the loop).
  - Total gate charge / input capacitance: low, &lt;=200 pF preferred so the op-amp can drive the gate without instability.
  - Low gate leakage and low drain leakage in the off state (output must reach &lt;&lt;1 uA when commanded off).
  - Operating temperature: -40 C to +85 C minimum.
 Quantity: 2 units required.
-Package: SOT-23, SOT-323, SC-70, or smaller. Single-transistor part preferred (no integrated diodes or dual devices).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+Package: SOT-23, SOT-323, SOT-666, SC-70, or smaller. Single-transistor part preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -997,7 +918,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>V-to-I sense resistor; sets I_FS = V_DAC / R_sense</t>
+          <t>V-to-I sense resistor; sets I_FS = (3.3V - V_DAC) / R_sense</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1010,38 +931,26 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>TNPW06035K11BEEA</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/795d1f84-2210-4cc0-96cc-0f19ebd34a16</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Resized for PMOS high-side topology. I = (3.3V - V_DAC) / R_sense. I_FS at V_DAC=0: 3.3V/5.11k = 646 uA. I_min at V_DAC=3.3V: 0 uA. 12-bit step ~= 0.16 uA at full range. Replaces 3.16 kOhm sized for NMOS low-side.</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Select a precision thin-film chip resistor used as a V-to-I sense element in a transconductance bias loop (high-side PMOS topology).
+          <t>Select a precision thin-film chip resistor used as a V-to-I sense element in a high-side PMOS transconductance bias loop.
 Requirements:
  - Value: 5.11 kOhm exact (E96 series).
  - Tolerance: 0.1% maximum.
  - Temperature coefficient: &lt;=25 ppm/C.
  - Construction: thin-film (not thick-film).
- - Power rating: &gt;=1/10 W (typical 0603); dissipates ~3.3V * 640uA = 2.1 mW max.
+ - Power rating: &gt;=1/10 W (typical 0603); max dissipation = 3.3V * 646uA = 2.1 mW.
  - Package: 0603 preferred; 0402 acceptable if 0.1% / 25 ppm available.
  - Operating temperature: -40 C to +85 C minimum.
-Context: I_FS = V_supply / R_sense = 3.3 V / 5.11 kOhm ~= 646 uA over 0-3.3V V_DAC range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="192" customHeight="1">
+Context: programs full-scale bias current at I_FS = V_supply / R_sense = 3.3 V / 5.11 kOhm ~= 646 uA over a 0-3.3V V_DAC range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1060,12 +969,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Series enable FET for hard hardware isolation of bias output; gated by MCU GPIO (pulled low at reset)</t>
+          <t>Optional series enable FET between PMOS drain and BIASx jumper; hard isolation</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Same as Q1/Q2 NMOS</t>
+          <t>Vgs(th) &lt;= 2 V, Vds &gt;= 6 V</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1078,20 +987,16 @@
           <t>2N7002</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Optional / DNP. Series NMOS pass switch between Q1/Q2 PMOS drain and BIASx jumper. GPIO low at reset -&gt; NMOS off -&gt; hard output isolation independent of MCP4728 EEPROM state. Uses same 2N7002 as last-resort Q1/Q2 footprint stuffing.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="120" customHeight="1">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Optional / DNP. Series NMOS pass switch between Q1/Q2 PMOS drain and BIASx jumper. GPIO low at reset -&gt; NMOS off -&gt; hard output isolation independent of MCP4728 EEPROM state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="180" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1123,32 +1028,16 @@
           <t>edge or vertical TH</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>HRM(G)-300-467B-1</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/675f9e44-e5e9-42eb-b3cf-486bb0d9fd1c</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>voltai originally misreported parts with incorrect form fit. Linear submitted</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Select a board-mount SMA connector (RF coaxial, 50 ohm).
 Mechanical:
  - Mount style: edge-launch end-launch OR through-hole vertical PCB mount, both acceptable.
- - Gender: female receptacle (jack) — mates with standard SMA male plug cables.
+ - Gender: female receptacle (jack) - mates with standard SMA male plug cables.
  - Compatible with 1.6 mm to 2.4 mm PCB thickness.
  - Body material: stainless steel or brass with nickel or stainless plating.
  - Center contact: gold plated.
@@ -1163,7 +1052,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="96" customHeight="1">
+    <row r="12" ht="192" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1195,26 +1084,10 @@
           <t>FMC LPC, SMT</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>ASP-134606-01</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/40f6d198-5134-4631-b282-00b3c277e681</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>claude + voltai explicitely agree</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Select the mezzanine-side connector for a VITA 57.1 FMC LPC daughtercard.
@@ -1227,7 +1100,7 @@
  - Must mate with the FMC LPC socket on a Digilent Genesys 2 carrier board.
 Mount:
  - Surface-mount on the bottom side of the mezzanine PCB.
- - Standard FMC stack height (8.5 mm or 10 mm). Confirm Genesys 2 compatibility — Genesys 2 typically expects 8.5 mm.
+ - Standard FMC stack height (8.5 mm or 10 mm). Confirm Genesys 2 compatibility - Genesys 2 typically expects 8.5 mm.
 Electrical:
  - Signal-pair speed rating: &gt;=10 Gbps per differential pair (per VITA 57.1 LPC).
  - Power pin current rating per VITA 57.1 (&gt;=2 A per power contact typical).
@@ -1236,7 +1109,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="108" customHeight="1">
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1268,22 +1141,10 @@
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TSW-104-05-G-S </t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/0392393d-3cf6-4da0-84d7-844a046d3b4a</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Select a 1x4 single-row male pin header.
@@ -1299,7 +1160,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="108" customHeight="1">
+    <row r="14" ht="96" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1331,26 +1192,10 @@
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Samtec TSW-102-05-G-S</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>https://suddendocs.samtec.com/catalog_english/tsw_th.pdf</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/ff158635-ccae-4b2a-bb23-3b555f7c5980</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Same as TSW-104-05-G-S </t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Select a 1x2 (2-position, 1-row) male pin header AND its mating shunt cap.
@@ -1396,18 +1241,10 @@
           <t>0603 or 0805</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Murata GRM21BR71A106KA73L</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
@@ -1422,7 +1259,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="72" customHeight="1">
+    <row r="16" ht="108" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1454,18 +1291,10 @@
           <t>0402 or 0603</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Murata GRM155R70J105KA12D</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
@@ -1480,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="84" customHeight="1">
+    <row r="17" ht="108" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1512,18 +1341,10 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Murata GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/89f805e6-698a-4848-9a9a-1216552ff551</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
@@ -1538,7 +1359,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="84" customHeight="1">
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1570,18 +1391,10 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>CRCW04020000Z0ED</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/e48a1fc5-00ab-4e0e-bf42-722ef3d0c8b3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Select 0 ohm chip jumper resistors.
@@ -1593,7 +1406,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="112" customHeight="1">
+    <row r="19" ht="84" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1625,18 +1438,10 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>CR0402-FX-1002GLF</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/a7abae63-cf40-4112-8c64-a6d94005f3d7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Select 10 kOhm chip pull-up / pull-down resistors.
@@ -1649,7 +1454,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="84" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1681,31 +1486,2956 @@
           <t>TH loop</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Keystone 5011</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>https://agent2.demo.voltai.ai/GLOBAL/admin/chat/c83ca0b9-08f0-4eb9-ac52-96f2abbe4c17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>claude suggested better part for this Keystone 5011 ×4</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Select PCB-mount GND test points / test loops.
  - Mount: through-hole.
  - Compatible with standard 0.1-inch oscilloscope probe ground spring clips and standard mini-grabber clip leads.
- - Loop style or turret pin style — both acceptable.
+ - Loop style or turret pin style - both acceptable.
  - Color coding: black (GND) preferred where available, otherwise unmarked is fine.
  - Current rating: not critical (probing only).
  - Quantity: 4 distributed across the board for easy probe access.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Part ref</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>10uF</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GRM21BR71A106KA73L</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 10 µF, X7R, 10 V, 0805</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>10nF</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71H103KA88D</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 10 nF, X7R, 50 V, 0402</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>22uF</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GRM21BR61A226ME44L</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 22 µF, X5R, 10 V, 0805</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R70J105KA12D</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R70J105KA12D</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R70J105KA12D</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R70J105KA12D</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1uF</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R70J105KA12D</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>eeprom</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C40</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C42</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C43</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>0.1uF</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>FMC LPC (C)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ASP-134606-01</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>FMC LPC (D)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ASP-134606-01</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>FMC LPC (G)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ASP-134606-01</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>FMC LPC (H)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ASP-134606-01</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1x2 100mil</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>TSW-102-05-G-S</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1x2 100mil</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>TSW-102-05-G-S</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1x2 100mil</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>TSW-102-05-G-S</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>J50</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>J51</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>J52</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>J53</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>J54</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>J55</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>J56</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>HRM-G-300-467B-1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>J57</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1x4 100mil</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TSW-104-05-G-S</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Header, 1×4, 2.54 mm pitch, TH vertical</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q40</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>PMZ1200UPEYL</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PMZ1200UPEYL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>MOSFET, P-channel, 20 V, SOT-666</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q41</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>PMZ1200UPEYL</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PMZ1200UPEYL</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>MOSFET, P-channel, 20 V, SOT-666</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q42</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q43</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2N7002</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1k</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1001GLF</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 1 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>R31</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>R33</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>R40</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>5.11k 0.1%</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>TNPW06035K11BEEA</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 5.11 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>R41</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>5.11k 0.1%</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>TNPW06035K11BEEA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 5.11 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>R42</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>R43</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>R44</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>R45</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-1002GLF</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>R50</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>R51</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>R52</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>R60</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2.2k</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-2201GLF</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>eeprom</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>R61</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2.2k</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>CR0402-FX-2201GLF</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>eeprom</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>R100</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>R101</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>R102</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>R104</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>R105</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>R106</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>R107</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>R108</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>R109</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>R110</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>R111</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>R112</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>R113</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>R114</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>R115</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>R116</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>R117</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>R118</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>R119</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>R120</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>R121</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>R122</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>R123</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>R124</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>R125</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>R126</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>R127</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CRCW04020000Z0ED</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Resistor, 0 Ω jumper, 0402</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>fmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TP50</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>GND-CLIP</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Keystone-5011</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Test point, GND test clip / loop, TH</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>TP51</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>GND-CLIP</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Keystone-5011</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Test point, GND test clip / loop, TH</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TP52</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>GND-CLIP</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Keystone-5011</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Test point, GND test clip / loop, TH</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>connectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>TPS7A8401A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>TPS7A8401A</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>LDO, 3 A, ANY-OUT programmable output, VQFN-20</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>TPS22916</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>TPS22916CNYFPR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Load switch, 1-channel, 5.5 V / 2 A, WCSP</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>U20</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Bobcat</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Bobcat</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Bobcat DUT — custom 40-QFN test chip (5×5 mm, 0.4 mm pitch, EP=GND)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>bobcat</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>U30</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>24AA08</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>24AA08-I-SN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>EEPROM, 8 Kbit I²C, SOIC-8</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>eeprom</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>U40</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>MCP4728</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>MCP4728</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>DAC, quad 12-bit voltage-output, I²C, MSOP-10</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>U41</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>OPA2388</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>OPA2388</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Op-amp, dual precision RRIO, zero-drift, MSOP-8</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
         </is>
       </c>
     </row>

--- a/test1/test1_bom.xlsx
+++ b/test1/test1_bom.xlsx
@@ -875,7 +875,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>SOT-23 or SOT-666</t>
+          <t>SOT883 / SOT-23 or smaller</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Resistor 5.11 kOhm precision</t>
+          <t>Resistor 3.65 kOhm precision</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5.11 kOhm, 0.1%, 25 ppm/C, thin-film</t>
+          <t>3.65 kOhm, 0.1%, 25 ppm/C, thin-film</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -939,14 +939,14 @@
         <is>
           <t>Select a precision thin-film chip resistor used as a V-to-I sense element in a high-side PMOS transconductance bias loop.
 Requirements:
- - Value: 5.11 kOhm exact (E96 series).
+ - Value: 3.65 kOhm exact (E96 series). (Lowered from 5.11 kOhm on 2026-05-30: at 5.11 kOhm the regulated full-scale capped at ~484 uA, failing the &gt;=640 uA spec because I*R left no headroom over the 0.5 V DUT compliance.)
  - Tolerance: 0.1% maximum.
  - Temperature coefficient: &lt;=25 ppm/C.
  - Construction: thin-film (not thick-film).
- - Power rating: &gt;=1/10 W (typical 0603); max dissipation = 3.3V * 646uA = 2.1 mW.
+ - Power rating: &gt;=1/10 W (typical 0603); max dissipation = 3.3V * ~900uA ~= 3 mW.
  - Package: 0603 preferred; 0402 acceptable if 0.1% / 25 ppm available.
  - Operating temperature: -40 C to +85 C minimum.
-Context: programs full-scale bias current at I_FS = V_supply / R_sense = 3.3 V / 5.11 kOhm ~= 646 uA over a 0-3.3V V_DAC range.</t>
+Context: programs full-scale bias current at I_FS = (V_supply - V_DUT) / R_sense; with 3.65 kOhm the regulated full-scale clears the &gt;=640 uA target inside the 0.5 V compliance window.</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1769,61 +1769,61 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM21BR61A226ME44L</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+          <t>MLCC, 22 µF, X5R, 10 V, 0805</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>10nF</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>GRM155R70J105KA12D</t>
+          <t>GRM155R71H103KA88D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+          <t>MLCC, 10 nF, X7R, 50 V, 0402</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1850,22 +1850,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R70J105KA12D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1904,22 +1904,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>GRM155R70J105KA12D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1958,22 +1958,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R70J105KA12D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
+          <t>MLCC, 1 µF, X7R, 6.3 V, 0402</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2086,14 +2086,14 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2113,14 +2113,14 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2147,66 +2147,66 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (C)</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (D)</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+          <t>MLCC, 100 nF, X7R, 16 V, 0402</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (G)</t>
+          <t>FMC LPC (C)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (H)</t>
+          <t>FMC LPC (D)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2255,61 +2255,61 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>J10</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1x2 100mil</t>
+          <t>FMC LPC (G)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TSW-102-05-G-S</t>
+          <t>ASP-134606-01</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>J11</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1x2 100mil</t>
+          <t>FMC LPC (H)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>TSW-102-05-G-S</t>
+          <t>ASP-134606-01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>J12</t>
+          <t>J10</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2336,61 +2336,61 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>J50</t>
+          <t>J11</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>1x2 100mil</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>HRM-G-300-467B-1</t>
+          <t>TSW-102-05-G-S</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>J51</t>
+          <t>J12</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>1x2 100mil</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>HRM-G-300-467B-1</t>
+          <t>TSW-102-05-G-S</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>J52</t>
+          <t>J50</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>J53</t>
+          <t>J51</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>J54</t>
+          <t>J52</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>J55</t>
+          <t>J53</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>J56</t>
+          <t>J54</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2525,22 +2525,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>J57</t>
+          <t>J55</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1x4 100mil</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>TSW-104-05-G-S</t>
+          <t>HRM-G-300-467B-1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×4, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2552,76 +2552,76 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>J56</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>HRM-G-300-467B-1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, P-channel, 20 V, SOT-666</t>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>J57</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>1x4 100mil</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>TSW-104-05-G-S</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, P-channel, 20 V, SOT-666</t>
+          <t>Header, 1×4, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q40</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2633,22 +2633,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q41</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2660,61 +2660,61 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Q42</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>MOSFET, N-channel, 60 V, SOT-23</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Q43</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>2N7002</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>MOSFET, N-channel, 60 V, SOT-23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2741,22 +2741,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1001GLF</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 1 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2768,76 +2768,76 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-1001GLF</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 1 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2849,22 +2849,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3146,76 +3146,76 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>5.11k 0.1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TNPW06035K11BEEA</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 5.11 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>5.11k 0.1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>TNPW06035K11BEEA</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 5.11 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.65k 0.1%</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>TNPW06033K65BEEA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 3.65 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3227,22 +3227,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.65k 0.1%</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>TNPW06033K65BEEA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 3.65 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3254,22 +3254,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3281,22 +3281,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>R45</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3308,61 +3308,61 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R44</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>R51</t>
+          <t>R45</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>R52</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3389,115 +3389,115 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>R60</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2.2k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-2201GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R61</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2.2k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-2201GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>R100</t>
+          <t>R60</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-2201GLF</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>R101</t>
+          <t>R61</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-2201GLF</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>R102</t>
+          <t>R100</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>R103</t>
+          <t>R101</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>R104</t>
+          <t>R102</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>R105</t>
+          <t>R103</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>R107</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>R111</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>R112</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>R113</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>R115</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>R117</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>R118</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R117</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>R120</t>
+          <t>R118</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>R121</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>R122</t>
+          <t>R120</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>R123</t>
+          <t>R121</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>R124</t>
+          <t>R122</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>R125</t>
+          <t>R123</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>R126</t>
+          <t>R124</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>R127</t>
+          <t>R125</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4199,61 +4199,61 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TP50</t>
+          <t>R126</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GND-CLIP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Keystone-5011</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Test point, GND test clip / loop, TH</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TP51</t>
+          <t>R127</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>GND-CLIP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Keystone-5011</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Test point, GND test clip / loop, TH</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TP52</t>
+          <t>TP50</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4280,160 +4280,214 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>TP51</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>TPS7A8401A</t>
+          <t>GND-CLIP</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>TPS7A8401A</t>
+          <t>Keystone-5011</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>LDO, 3 A, ANY-OUT programmable output, VQFN-20</t>
+          <t>Test point, GND test clip / loop, TH</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>TP52</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>TPS22916</t>
+          <t>GND-CLIP</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>TPS22916CNYFPR</t>
+          <t>Keystone-5011</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Load switch, 1-channel, 5.5 V / 2 A, WCSP</t>
+          <t>Test point, GND test clip / loop, TH</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>TPS7A8401A</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Bobcat</t>
+          <t>TPS7A8401A</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Bobcat DUT — custom 40-QFN test chip (5×5 mm, 0.4 mm pitch, EP=GND)</t>
+          <t>LDO, 3 A, ANY-OUT programmable output, VQFN-20</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>U30</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>24AA08</t>
+          <t>TPS22916</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>24AA08-I-SN</t>
+          <t>TPS22916CNYFPR</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>EEPROM, 8 Kbit I²C, SOIC-8</t>
+          <t>Load switch, 1-channel, 5.5 V / 2 A, WCSP</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>U40</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>MCP4728</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>MCP4728</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>DAC, quad 12-bit voltage-output, I²C, MSOP-10</t>
+          <t>Bobcat DUT — custom 40-QFN test chip (5×5 mm, 0.4 mm pitch, EP=GND)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>U30</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>24AA08</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>24AA08-I-SN</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>EEPROM, 8 Kbit I²C, SOIC-8</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>eeprom</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>U40</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>MCP4728</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>MCP4728</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>DAC, quad 12-bit voltage-output, I²C, MSOP-10</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
           <t>U41</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>OPA2388</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>OPA2388</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Op-amp, dual precision RRIO, zero-drift, MSOP-8</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Op-amp, dual precision RRIO, zero-drift, VSSOP-8 (DGK)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>bias</t>
         </is>

--- a/test1/test1_bom.xlsx
+++ b/test1/test1_bom.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -950,89 +950,43 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="180" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Qen1, Qen2 (DNP)</t>
+          <t>J1-J7</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NMOS enable FET (DNP)</t>
+          <t>RF connector</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Optional series enable FET between PMOS drain and BIASx jumper; hard isolation</t>
+          <t>Board-mount SMA jack, 50 ohm, DC-6 GHz</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Vgs(th) &lt;= 2 V, Vds &gt;= 6 V</t>
+          <t>SMA female, 50 ohm</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2N7002</t>
-        </is>
-      </c>
+          <t>edge or vertical TH</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Optional / DNP. Series NMOS pass switch between Q1/Q2 PMOS drain and BIASx jumper. GPIO low at reset -&gt; NMOS off -&gt; hard output isolation independent of MCP4728 EEPROM state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="180" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>J1-J7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>RF connector</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Board-mount SMA jack, 50 ohm, DC-6 GHz</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>SMA female, 50 ohm</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>edge or vertical TH</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Select a board-mount SMA connector (RF coaxial, 50 ohm).
 Mechanical:
@@ -1052,43 +1006,43 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="192" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="11" ht="192" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>J8</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>FMC connector</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>VITA 57.1 FMC LPC mezzanine-side connector</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>160-pin LPC, 1.27 mm pitch</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>FMC LPC, SMT</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Select the mezzanine-side connector for a VITA 57.1 FMC LPC daughtercard.
 Standard:
@@ -1109,43 +1063,43 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>J9</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Pin header</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1x4 100-mil pin header for GPIO breakout</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1x4, 2.54 mm pitch</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Select a 1x4 single-row male pin header.
  - Pitch: 2.54 mm (100 mil).
@@ -1160,43 +1114,43 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="96" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>JP1-JPn</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Jumper header + shunt</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1x2 100-mil header with mating shunt cap</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1x2, 2.54 mm pitch</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>TH vertical</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Select a 1x2 (2-position, 1-row) male pin header AND its mating shunt cap.
  - Pitch: 2.54 mm (100 mil).
@@ -1209,43 +1163,43 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="14" ht="108" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>C_bulk*</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Bulk MLCC</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>10 uF X7R bulk decoupling, one per Bobcat supply pin bank</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>10 uF, X7R, &gt;=6.3 V</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0603 or 0805</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1259,43 +1213,43 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="108" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="15" ht="108" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>C_mid*</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mid MLCC</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1 uF X7R mid-band decoupling, one per Bobcat supply pin bank</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1 uF, X7R, &gt;=6.3 V</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>0402 or 0603</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1309,43 +1263,43 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="108" customHeight="1">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="16" ht="108" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>C_hf*</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>HF MLCC</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>100 nF X7R high-frequency decoupling, one per Bobcat supply pin bank</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>100 nF, X7R, &gt;=6.3 V</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Select MLCC bypass capacitors for digital power-rail decoupling.
 Three-value bank per Bobcat power pin (10 uF + 1 uF + 100 nF):
@@ -1359,43 +1313,43 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>R0*</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Resistor 0 ohm</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Series 0 ohm jumpers on FMC LA signals and analog rails</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>0 ohm</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Select 0 ohm chip jumper resistors.
  - Value: 0 ohm.
@@ -1406,43 +1360,43 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+    <row r="18" ht="84" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>R10k*</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C18" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Resistor 10 kOhm</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Pull-up / pull-down resistors on digital control lines</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>10 kOhm, 5%</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Select 10 kOhm chip pull-up / pull-down resistors.
  - Value: 10 kOhm.
@@ -1454,43 +1408,43 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="84" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+    <row r="19" ht="84" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>TP1-TP4</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Test point</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>GND test clips / loops</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>GND probe point</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>TH loop</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Select PCB-mount GND test points / test loops.
  - Mount: through-hole.
@@ -1513,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2201,93 +2155,93 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>C44</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (C)</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
+          <t>GRM21BR71A106KA73L</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+          <t>MLCC, 10 µF, X7R, 10 V, 0805</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (D)</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
+          <t>GRM21BR71A106KA73L</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+          <t>MLCC, 10 µF, X7R, 10 V, 0805</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>C46</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (G)</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ASP-134606-01</t>
+          <t>GRM21BR71A106KA73L</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
+          <t>MLCC, 10 µF, X7R, 10 V, 0805</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FMC LPC (H)</t>
+          <t>FMC LPC (C)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2309,169 +2263,169 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>J10</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1x2 100mil</t>
+          <t>FMC LPC (D)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TSW-102-05-G-S</t>
+          <t>ASP-134606-01</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>J11</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1x2 100mil</t>
+          <t>FMC LPC (G)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TSW-102-05-G-S</t>
+          <t>ASP-134606-01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>J12</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1x2 100mil</t>
+          <t>FMC LPC (H)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TSW-102-05-G-S</t>
+          <t>ASP-134606-01</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, VITA 57.1 FMC LPC mezzanine, 160-pos SMT</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>J50</t>
+          <t>J10</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>1x2 100mil</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>HRM-G-300-467B-1</t>
+          <t>TSW-102-05-G-S</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>J51</t>
+          <t>J11</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>1x2 100mil</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>HRM-G-300-467B-1</t>
+          <t>TSW-102-05-G-S</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>J52</t>
+          <t>J12</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>1x2 100mil</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>HRM-G-300-467B-1</t>
+          <t>TSW-102-05-G-S</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
+          <t>Header, 1×2, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>J53</t>
+          <t>J50</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2498,7 +2452,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>J54</t>
+          <t>J51</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2525,7 +2479,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>J55</t>
+          <t>J52</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2552,7 +2506,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>J56</t>
+          <t>J53</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2579,22 +2533,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>J57</t>
+          <t>J54</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1x4 100mil</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TSW-104-05-G-S</t>
+          <t>HRM-G-300-467B-1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Header, 1×4, 2.54 mm pitch, TH vertical</t>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2606,103 +2560,103 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>J55</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>HRM-G-300-467B-1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>J56</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PMZ1200UPEYL</t>
+          <t>HRM-G-300-467B-1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
+          <t>Connector, SMA jack, 50 Ω, edge-launch</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>J57</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>1x4 100mil</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>TSW-104-05-G-S</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+          <t>Header, 1×4, 2.54 mm pitch, TH vertical</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q40</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2N7002</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>MOSFET, N-channel, 60 V, SOT-23</t>
+          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2714,34 +2668,34 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Q41</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>PMZ1200UPEYL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>MOSFET, P-channel, 20 V, SOT883 (DFN1006-3)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2768,7 +2722,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2795,22 +2749,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1001GLF</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 1 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2822,34 +2776,34 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-1001GLF</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 1 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>bobcat</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2876,22 +2830,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2903,7 +2857,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2930,7 +2884,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2957,7 +2911,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2984,7 +2938,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3011,7 +2965,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3038,7 +2992,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3065,7 +3019,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3092,7 +3046,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3119,7 +3073,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3146,7 +3100,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3173,7 +3127,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3200,34 +3154,34 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>3.65k 0.1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>TNPW06033K65BEEA</t>
+          <t>CR0402-FX-1002GLF</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 3.65 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
+          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3254,22 +3208,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.65k 0.1%</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>TNPW06033K65BEEA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 3.65 kΩ, 0.1%, 25 ppm/°C, thin-film, 0603</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3281,7 +3235,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3301,122 +3255,122 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>R45</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-1002GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 10 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>bias</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R60</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-2201GLF</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>R51</t>
+          <t>R61</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.2k</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>CR0402-FX-2201GLF</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R52</t>
+          <t>R100</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3436,68 +3390,68 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>R60</t>
+          <t>R101</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2.2k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-2201GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>R61</t>
+          <t>R102</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2.2k</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CR0402-FX-2201GLF</t>
+          <t>CRCW04020000Z0ED</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 2.2 kΩ, 1%, 1/16 W, 0402</t>
+          <t>Resistor, 0 Ω jumper, 0402</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>eeprom</t>
+          <t>fmc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>R100</t>
+          <t>R103</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3524,7 +3478,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>R101</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3551,7 +3505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>R102</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3578,7 +3532,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>R103</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3605,7 +3559,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>R104</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3632,7 +3586,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>R105</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3659,7 +3613,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>R106</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3686,7 +3640,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>R107</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3713,7 +3667,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>R108</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -3740,7 +3694,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>R109</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -3767,7 +3721,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>R110</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -3794,7 +3748,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>R111</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -3821,7 +3775,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>R112</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -3848,7 +3802,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>R113</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -3875,7 +3829,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>R114</t>
+          <t>R117</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -3902,7 +3856,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>R115</t>
+          <t>R118</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -3929,7 +3883,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>R116</t>
+          <t>R119</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -3956,7 +3910,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>R117</t>
+          <t>R122</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -3983,7 +3937,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>R118</t>
+          <t>R123</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4010,7 +3964,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>R119</t>
+          <t>R124</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4037,7 +3991,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>R120</t>
+          <t>R125</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4064,7 +4018,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>R121</t>
+          <t>R126</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4091,7 +4045,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>R122</t>
+          <t>R127</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4118,376 +4072,241 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>R123</t>
+          <t>TP50</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>GND-CLIP</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>Keystone-5011</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Test point, GND test clip / loop, TH</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>R124</t>
+          <t>TP51</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>GND-CLIP</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>Keystone-5011</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Test point, GND test clip / loop, TH</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>R125</t>
+          <t>TP52</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>GND-CLIP</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>Keystone-5011</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Test point, GND test clip / loop, TH</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>connectors</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>R126</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>TPS7A8401A</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>TPS7A8401A</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>LDO, 3 A, ANY-OUT programmable output, VQFN-20</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>R127</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>TPS22916</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CRCW04020000Z0ED</t>
+          <t>TPS22916CNYFPR</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Resistor, 0 Ω jumper, 0402</t>
+          <t>Load switch, 1-channel, 5.5 V / 2 A, WCSP</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>fmc</t>
+          <t>power</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TP50</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>GND-CLIP</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Keystone-5011</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Test point, GND test clip / loop, TH</t>
+          <t>Bobcat DUT — custom 40-QFN test chip (5×5 mm, 0.4 mm pitch, EP=GND)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>bobcat</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TP51</t>
+          <t>U30</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>GND-CLIP</t>
+          <t>24AA08</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Keystone-5011</t>
+          <t>24AA08-I-SN</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Test point, GND test clip / loop, TH</t>
+          <t>EEPROM, 8 Kbit I²C, SOIC-8</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>eeprom</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TP52</t>
+          <t>U40</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>GND-CLIP</t>
+          <t>MCP4728</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Keystone-5011</t>
+          <t>MCP4728</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Test point, GND test clip / loop, TH</t>
+          <t>DAC, quad 12-bit voltage-output, I²C, MSOP-10</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>connectors</t>
+          <t>bias</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U41</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>TPS7A8401A</t>
+          <t>OPA2388</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>TPS7A8401A</t>
+          <t>OPA2388</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>LDO, 3 A, ANY-OUT programmable output, VQFN-20</t>
+          <t>Op-amp, dual precision RRIO, zero-drift, VSSOP-8 (DGK)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>power</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>U11</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>TPS22916</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>TPS22916CNYFPR</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Load switch, 1-channel, 5.5 V / 2 A, WCSP</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>power</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>U20</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Bobcat</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Bobcat</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Bobcat DUT — custom 40-QFN test chip (5×5 mm, 0.4 mm pitch, EP=GND)</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>bobcat</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>U30</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>24AA08</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>24AA08-I-SN</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>EEPROM, 8 Kbit I²C, SOIC-8</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>eeprom</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>U40</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>MCP4728</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>MCP4728</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>DAC, quad 12-bit voltage-output, I²C, MSOP-10</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>bias</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>U41</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>OPA2388</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>OPA2388</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Op-amp, dual precision RRIO, zero-drift, VSSOP-8 (DGK)</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>bias</t>
         </is>
